--- a/templates/CAPITANIA BWM - template.xlsx
+++ b/templates/CAPITANIA BWM - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$42</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1278,14 +1278,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="19.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col width="19.7109375" customWidth="1" style="6" min="1" max="1"/>
     <col width="18.7109375" customWidth="1" style="6" min="2" max="6"/>
     <col hidden="1" width="13" customWidth="1" style="6" min="7" max="7"/>
-    <col width="19.7109375" customWidth="1" style="6" min="8" max="14"/>
-    <col width="19.7109375" customWidth="1" style="6" min="15" max="16384"/>
+    <col width="19.7109375" customWidth="1" style="6" min="8" max="15"/>
+    <col width="19.7109375" customWidth="1" style="6" min="16" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1" customFormat="1" s="2">
@@ -1429,98 +1429,98 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="48">
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="49" t="n">
-        <v>1.7477845</v>
+        <v>1.7616433</v>
       </c>
       <c r="D17" s="34" t="n">
-        <v>-0.0003619273270746293</v>
+        <v>0.000463873073241361</v>
       </c>
       <c r="E17" s="34" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>-0.6669475420552964</v>
+        <v>0.8548097446097745</v>
       </c>
       <c r="H17" s="50" t="n"/>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="48">
       <c r="B18" s="51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="52" t="n">
-        <v>1.7484173</v>
+        <v>1.7608265</v>
       </c>
       <c r="D18" s="45" t="n">
-        <v>-0.007509903657775707</v>
+        <v>0.0001441008290028467</v>
       </c>
       <c r="E18" s="45" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="46" t="n">
-        <v>-13.83899863574765</v>
+        <v>0.2655441756454102</v>
       </c>
       <c r="H18" s="53" t="n"/>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="48">
       <c r="B19" s="51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="52" t="n">
-        <v>1.7616471</v>
+        <v>1.7605728</v>
       </c>
       <c r="D19" s="45" t="n">
-        <v>1.135301290755564e-07</v>
+        <v>0.00110859449596723</v>
       </c>
       <c r="E19" s="45" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="46" t="n">
-        <v>0.0002092095149271492</v>
+        <v>2.042880763377438</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="48">
       <c r="B20" s="51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="52" t="n">
-        <v>1.7616469</v>
+        <v>1.7586232</v>
       </c>
       <c r="D20" s="45" t="n">
-        <v>0.0009414258035556067</v>
+        <v>-0.001551418515214342</v>
       </c>
       <c r="E20" s="45" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="46" t="n">
-        <v>1.73482790256226</v>
+        <v>-2.85890201711109</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="48">
       <c r="B21" s="51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="52" t="n">
-        <v>1.75999</v>
+        <v>1.7613558</v>
       </c>
       <c r="D21" s="45" t="n">
-        <v>0.0003679214970455646</v>
+        <v>0.002132386865125069</v>
       </c>
       <c r="E21" s="45" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="46" t="n">
-        <v>0.6779933974790641</v>
+        <v>3.929491011086069</v>
       </c>
     </row>
     <row r="22" ht="15.95" customHeight="1">
@@ -1561,18 +1561,18 @@
       <c r="A24" s="7" t="n"/>
       <c r="B24" s="36" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="36" t="inlineStr"/>
       <c r="D24" s="34" t="n">
-        <v>-0.002062582159418014</v>
+        <v>0.005655933463931451</v>
       </c>
       <c r="E24" s="34" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>-0.19674805506607</v>
+        <v>1.486515571979031</v>
       </c>
       <c r="G24" s="15" t="n"/>
     </row>
@@ -1585,13 +1585,13 @@
       </c>
       <c r="C25" s="44" t="inlineStr"/>
       <c r="D25" s="45" t="n">
-        <v>0.0005526044137824648</v>
+        <v>0.002343979771083582</v>
       </c>
       <c r="E25" s="45" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F25" s="46" t="n">
-        <v>0.04764712188574193</v>
+        <v>0.2036397977372851</v>
       </c>
       <c r="G25" s="47" t="n"/>
     </row>
@@ -1604,13 +1604,13 @@
       </c>
       <c r="C26" s="44" t="inlineStr"/>
       <c r="D26" s="45" t="n">
-        <v>0.02351948947018201</v>
+        <v>0.02657419179228193</v>
       </c>
       <c r="E26" s="45" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F26" s="46" t="n">
-        <v>0.6664984598360888</v>
+        <v>0.7549774580680455</v>
       </c>
       <c r="G26" s="47" t="n"/>
     </row>
@@ -1623,13 +1623,13 @@
       </c>
       <c r="C27" s="44" t="inlineStr"/>
       <c r="D27" s="45" t="n">
-        <v>0.05347115736990316</v>
+        <v>0.05790906913736649</v>
       </c>
       <c r="E27" s="45" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F27" s="46" t="n">
-        <v>0.7440205415539125</v>
+        <v>0.8068115883757109</v>
       </c>
       <c r="G27" s="47" t="n"/>
     </row>
@@ -1642,13 +1642,13 @@
       </c>
       <c r="C28" s="44" t="inlineStr"/>
       <c r="D28" s="45" t="n">
-        <v>0.1320100007409493</v>
+        <v>0.1356150581330884</v>
       </c>
       <c r="E28" s="45" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F28" s="46" t="n">
-        <v>0.8930640641439668</v>
+        <v>0.9162186851996992</v>
       </c>
       <c r="G28" s="47" t="n"/>
     </row>
@@ -1656,18 +1656,18 @@
       <c r="A29" s="7" t="n"/>
       <c r="B29" s="44" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C29" s="44" t="inlineStr"/>
       <c r="D29" s="45" t="n">
-        <v>0.01958450308815274</v>
+        <v>0.2697524872402597</v>
       </c>
       <c r="E29" s="45" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F29" s="46" t="n">
-        <v>0.6037327925318283</v>
+        <v>0.9705754400725762</v>
       </c>
       <c r="G29" s="47" t="n"/>
     </row>
@@ -1675,18 +1675,18 @@
       <c r="A30" s="7" t="n"/>
       <c r="B30" s="44" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C30" s="44" t="inlineStr"/>
       <c r="D30" s="45" t="n">
-        <v>0.1468103957985647</v>
+        <v>0.02766914836987833</v>
       </c>
       <c r="E30" s="45" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F30" s="46" t="n">
-        <v>1.025693942258333</v>
+        <v>0.7270757843650827</v>
       </c>
       <c r="G30" s="47" t="n"/>
     </row>
@@ -1694,18 +1694,18 @@
       <c r="A31" s="7" t="n"/>
       <c r="B31" s="44" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr"/>
       <c r="D31" s="45" t="n">
-        <v>0.1265108165026048</v>
+        <v>0.1468103957985647</v>
       </c>
       <c r="E31" s="45" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F31" s="46" t="n">
-        <v>1.158471697492812</v>
+        <v>1.025693942258333</v>
       </c>
       <c r="G31" s="47" t="n"/>
     </row>
@@ -1713,171 +1713,190 @@
       <c r="A32" s="7" t="n"/>
       <c r="B32" s="44" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C32" s="44" t="inlineStr"/>
       <c r="D32" s="45" t="n">
-        <v>0.7477845000000001</v>
+        <v>0.1265108165026048</v>
       </c>
       <c r="E32" s="45" t="n">
-        <v>0.696661144481928</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F32" s="46" t="n">
-        <v>1.073383388643111</v>
+        <v>1.158471697492812</v>
       </c>
       <c r="G32" s="47" t="n"/>
     </row>
     <row r="33" ht="15.95" customHeight="1">
       <c r="A33" s="7" t="n"/>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="26.1" customHeight="1">
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="inlineStr"/>
+      <c r="D33" s="45" t="n">
+        <v>0.7616433</v>
+      </c>
+      <c r="E33" s="45" t="n">
+        <v>0.7058908021152912</v>
+      </c>
+      <c r="F33" s="46" t="n">
+        <v>1.078981759951595</v>
+      </c>
+      <c r="G33" s="47" t="n"/>
+    </row>
+    <row r="34" ht="15.95" customHeight="1">
       <c r="A34" s="7" t="n"/>
-      <c r="B34" s="37" t="inlineStr">
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="13" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="26.1" customHeight="1">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C34" s="37" t="n"/>
-      <c r="D34" s="37" t="n"/>
-      <c r="E34" s="37" t="n"/>
-      <c r="F34" s="37" t="n"/>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="35" t="n">
-        <v>106059997.0543</v>
-      </c>
-      <c r="F35" s="35" t="n"/>
+      <c r="C35" s="37" t="n"/>
+      <c r="D35" s="37" t="n"/>
+      <c r="E35" s="37" t="n"/>
+      <c r="F35" s="37" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="7" t="n"/>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="19" t="n"/>
       <c r="E36" s="35" t="n">
-        <v>119260533.6281317</v>
+        <v>105014025.5392</v>
       </c>
       <c r="F36" s="35" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="7" t="n"/>
-      <c r="B37" s="21" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="35" t="n">
+        <v>118805022.2679266</v>
+      </c>
+      <c r="F37" s="35" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
-      <c r="B38" s="22" t="inlineStr">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="15.95" customHeight="1">
+      <c r="B39" s="22" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="n"/>
-      <c r="E38" s="24" t="n"/>
-      <c r="F38" s="24" t="n"/>
-      <c r="G38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="23" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="24" t="n"/>
+      <c r="F39" s="24" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C39" s="25" t="inlineStr">
+      <c r="C40" s="25" t="inlineStr">
         <is>
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="D39" s="26" t="n"/>
-      <c r="E39" s="26" t="n"/>
-      <c r="F39" s="26" t="n"/>
-      <c r="G39" s="4" t="n"/>
-    </row>
-    <row r="40" ht="15.95" customHeight="1">
-      <c r="B40" s="27" t="n"/>
-      <c r="C40" s="28" t="n"/>
-      <c r="D40" s="29" t="n"/>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="29" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="26" t="n"/>
       <c r="G40" s="4" t="n"/>
     </row>
-    <row r="41" ht="63.75" customHeight="1">
-      <c r="B41" s="39" t="inlineStr">
+    <row r="41" ht="15.95" customHeight="1">
+      <c r="B41" s="27" t="n"/>
+      <c r="C41" s="28" t="n"/>
+      <c r="D41" s="29" t="n"/>
+      <c r="E41" s="29" t="n"/>
+      <c r="F41" s="29" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="63.75" customHeight="1">
+      <c r="B42" s="39" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="C41" s="39" t="n"/>
-      <c r="D41" s="39" t="n"/>
-      <c r="E41" s="39" t="n"/>
-      <c r="F41" s="39" t="n"/>
-      <c r="G41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="40" t="n"/>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="40" t="n"/>
-      <c r="E42" s="40" t="n"/>
-      <c r="F42" s="40" t="n"/>
+      <c r="C42" s="39" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="30" t="n"/>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="30" t="n"/>
-      <c r="E43" s="30" t="n"/>
-      <c r="F43" s="30" t="n"/>
+      <c r="B43" s="40" t="n"/>
+      <c r="C43" s="40" t="n"/>
+      <c r="D43" s="40" t="n"/>
+      <c r="E43" s="40" t="n"/>
+      <c r="F43" s="40" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="31" t="n"/>
-      <c r="C44" s="32" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="30" t="n"/>
+      <c r="C44" s="30" t="n"/>
+      <c r="D44" s="30" t="n"/>
+      <c r="E44" s="30" t="n"/>
+      <c r="F44" s="30" t="n"/>
       <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="4" t="n"/>
       <c r="B45" s="31" t="n"/>
       <c r="C45" s="32" t="n"/>
       <c r="D45" s="16" t="n"/>
       <c r="E45" s="16" t="n"/>
       <c r="F45" s="16" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="31" t="n"/>
+      <c r="C46" s="32" t="n"/>
+      <c r="D46" s="16" t="n"/>
+      <c r="E46" s="16" t="n"/>
+      <c r="F46" s="16" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="86" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="83"/>
 </worksheet>
 </file>